--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_25-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_25-01-2026.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>£9.77</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>£29.28 Pre Sale Price-£30.00</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>£31.63</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>£44.24</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>£40.45</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>£43.40</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
